--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:44:54+00:00</t>
+    <t>2023-05-08T13:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:51:23+00:00</t>
+    <t>2023-05-08T14:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:05:33+00:00</t>
+    <t>2023-05-08T14:07:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:07:06+00:00</t>
+    <t>2023-05-08T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:23:05+00:00</t>
+    <t>2023-05-08T14:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:48:00+00:00</t>
+    <t>2023-05-08T15:19:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:19:54+00:00</t>
+    <t>2023-05-08T15:31:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:31:47+00:00</t>
+    <t>2023-05-08T16:10:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T16:10:55+00:00</t>
+    <t>2023-05-08T18:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:38:59+00:00</t>
+    <t>2023-05-08T18:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:49:00+00:00</t>
+    <t>2023-05-08T19:06:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:06:08+00:00</t>
+    <t>2023-05-08T19:17:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:17:16+00:00</t>
+    <t>2023-05-08T19:36:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:36:32+00:00</t>
+    <t>2023-05-08T19:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:37:24+00:00</t>
+    <t>2023-05-08T19:39:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:39:41+00:00</t>
+    <t>2023-05-08T19:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:40:43+00:00</t>
+    <t>2023-05-08T19:42:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:42:22+00:00</t>
+    <t>2023-05-08T19:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:53:59+00:00</t>
+    <t>2023-05-08T20:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T20:00:55+00:00</t>
+    <t>2023-05-08T21:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:00:30+00:00</t>
+    <t>2023-05-08T21:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:01:17+00:00</t>
+    <t>2023-05-08T21:08:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:08:01+00:00</t>
+    <t>2023-05-09T07:17:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2243" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2241" uniqueCount="522">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T07:17:44+00:00</t>
+    <t>2023-05-09T15:00:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>4.3.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -274,6 +274,9 @@
     <t>Organization(classCode=ORG, determinerCode=INST)</t>
   </si>
   <si>
+    <t>administrative.group</t>
+  </si>
+  <si>
     <t>Organization.id</t>
   </si>
   <si>
@@ -357,7 +360,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
+    <t>IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -415,6 +418,10 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -468,6 +475,10 @@
 </t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
     <t>Organization.extension:DistrictIndex</t>
   </si>
   <si>
@@ -501,7 +512,7 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -561,201 +572,195 @@
     <t>Organization.identifier.id</t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.use</t>
+  </si>
+  <si>
+    <t>Organization.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.3.0</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type.coding</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type.coding.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.coding.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type.coding.system</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/v2-0203</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type.coding.version</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.coding.version</t>
+  </si>
+  <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.use</t>
-  </si>
-  <si>
-    <t>Organization.identifier.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this identifier, if known .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.use</t>
-  </si>
-  <si>
-    <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type.coding</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type.coding.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type.coding.system</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/v2-0203</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type.coding.version</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.version</t>
-  </si>
-  <si>
     <t>Version of the system - if relevant</t>
   </si>
   <si>
@@ -937,7 +942,7 @@
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
   </si>
   <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4B/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>123456</t>
@@ -1216,10 +1221,10 @@
     <t>home</t>
   </si>
   <si>
-    <t>The use of an address.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/address-use|4.0.1</t>
+    <t>The use of an address (home / work / etc.).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/address-use|4.3.0</t>
   </si>
   <si>
     <t>Address.use</t>
@@ -1243,7 +1248,7 @@
     <t>Distinguishes between physical addresses (those you can visit) and mailing addresses (e.g. PO Boxes and care-of addresses). Most addresses are both.</t>
   </si>
   <si>
-    <t>The definition of Address states that "address is intended to describe postal addresses, not physical locations". However, many applications track whether an address has a dual purpose of being a location that can be visited as well as being a valid delivery destination, and Postal addresses are often used as proxies for physical locations (also see the [Location](http://hl7.org/fhir/R4/location.html#) resource).</t>
+    <t>The definition of Address states that "address is intended to describe postal addresses, not physical locations". However, many applications track whether an address has a dual purpose of being a location that can be visited as well as being a valid delivery destination, and Postal addresses are often used as proxies for physical locations (also see the [Location](http://hl7.org/fhir/R4B/location.html#) resource).</t>
   </si>
   <si>
     <t>both</t>
@@ -1252,7 +1257,7 @@
     <t>The type of an address (physical / postal).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/address-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/address-type|4.3.0</t>
   </si>
   <si>
     <t>Address.type</t>
@@ -1504,6 +1509,10 @@
   </si>
   <si>
     <t>Need to keep track of assigned contact points within bigger organization.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+</t>
   </si>
   <si>
     <t>.contactParty</t>
@@ -1968,7 +1977,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="54.10546875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="43.6484375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -2216,15 +2225,15 @@
         <v>30</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2235,7 +2244,7 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>77</v>
@@ -2244,19 +2253,19 @@
         <v>77</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2306,13 +2315,13 @@
         <v>77</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>77</v>
@@ -2335,10 +2344,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2349,7 +2358,7 @@
         <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>77</v>
@@ -2358,16 +2367,16 @@
         <v>77</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2418,19 +2427,19 @@
         <v>77</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
@@ -2447,10 +2456,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2461,28 +2470,28 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2532,19 +2541,19 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
@@ -2561,10 +2570,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2575,7 +2584,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>77</v>
@@ -2587,16 +2596,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2622,13 +2631,13 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
@@ -2646,19 +2655,19 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
@@ -2675,21 +2684,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>77</v>
@@ -2701,16 +2710,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2760,25 +2769,25 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -2789,14 +2798,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2815,16 +2824,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2874,7 +2883,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2886,13 +2895,13 @@
         <v>77</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
@@ -2903,10 +2912,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2914,7 +2923,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>79</v>
@@ -2929,13 +2938,13 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2974,17 +2983,17 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2996,7 +3005,7 @@
         <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
@@ -3013,23 +3022,23 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>77</v>
@@ -3041,13 +3050,13 @@
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -3098,7 +3107,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -3107,10 +3116,10 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
@@ -3127,23 +3136,23 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>77</v>
@@ -3155,13 +3164,13 @@
         <v>77</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3212,7 +3221,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3221,10 +3230,10 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>77</v>
@@ -3241,14 +3250,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3261,25 +3270,25 @@
         <v>77</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -3328,7 +3337,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3340,13 +3349,13 @@
         <v>77</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>77</v>
@@ -3357,10 +3366,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3368,7 +3377,7 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>79</v>
@@ -3380,20 +3389,20 @@
         <v>77</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -3430,19 +3439,19 @@
         <v>77</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3451,43 +3460,43 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>77</v>
@@ -3496,20 +3505,20 @@
         <v>77</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
@@ -3558,7 +3567,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3567,30 +3576,30 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3601,7 +3610,7 @@
         <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>77</v>
@@ -3613,13 +3622,13 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>174</v>
+        <v>89</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3670,13 +3679,13 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>77</v>
@@ -3688,7 +3697,7 @@
         <v>77</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -3699,14 +3708,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3725,16 +3734,16 @@
         <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3772,19 +3781,19 @@
         <v>77</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3796,13 +3805,13 @@
         <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -3813,10 +3822,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3827,31 +3836,31 @@
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3876,13 +3885,11 @@
         <v>77</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>77</v>
@@ -3900,25 +3907,25 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3929,10 +3936,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3943,7 +3950,7 @@
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>77</v>
@@ -3952,22 +3959,22 @@
         <v>77</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3992,11 +3999,9 @@
         <v>77</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="Y18" t="s" s="2">
         <v>204</v>
       </c>
+      <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
         <v>205</v>
       </c>
@@ -4022,19 +4027,19 @@
         <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>207</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -4059,7 +4064,7 @@
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>77</v>
@@ -4071,13 +4076,13 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>174</v>
+        <v>89</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4128,13 +4133,13 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>77</v>
@@ -4146,7 +4151,7 @@
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -4164,7 +4169,7 @@
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4183,16 +4188,16 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4230,19 +4235,19 @@
         <v>77</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4254,13 +4259,13 @@
         <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -4294,7 +4299,7 @@
         <v>77</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
         <v>214</v>
@@ -4370,7 +4375,7 @@
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>220</v>
@@ -4401,7 +4406,7 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>77</v>
@@ -4413,13 +4418,13 @@
         <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>174</v>
+        <v>89</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4470,13 +4475,13 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>77</v>
@@ -4488,7 +4493,7 @@
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -4506,7 +4511,7 @@
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4525,16 +4530,16 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4572,19 +4577,19 @@
         <v>77</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4596,13 +4601,13 @@
         <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -4627,7 +4632,7 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>77</v>
@@ -4636,10 +4641,10 @@
         <v>77</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>228</v>
@@ -4706,13 +4711,13 @@
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>234</v>
@@ -4743,7 +4748,7 @@
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>77</v>
@@ -4752,19 +4757,19 @@
         <v>77</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4814,25 +4819,25 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4843,10 +4848,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4857,7 +4862,7 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>77</v>
@@ -4866,20 +4871,20 @@
         <v>77</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4889,7 +4894,7 @@
         <v>77</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>77</v>
@@ -4928,25 +4933,25 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4957,10 +4962,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4971,7 +4976,7 @@
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>77</v>
@@ -4980,20 +4985,20 @@
         <v>77</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -5003,7 +5008,7 @@
         <v>77</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>77</v>
@@ -5042,25 +5047,25 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -5071,10 +5076,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5085,7 +5090,7 @@
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>77</v>
@@ -5094,22 +5099,22 @@
         <v>77</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -5158,25 +5163,25 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -5187,10 +5192,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5201,7 +5206,7 @@
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>77</v>
@@ -5210,22 +5215,22 @@
         <v>77</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -5235,7 +5240,7 @@
         <v>77</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>77</v>
@@ -5274,25 +5279,25 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -5303,10 +5308,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5314,10 +5319,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>77</v>
@@ -5326,35 +5331,35 @@
         <v>77</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="U30" t="s" s="2">
         <v>77</v>
@@ -5390,28 +5395,28 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -5419,10 +5424,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5430,10 +5435,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>77</v>
@@ -5442,19 +5447,19 @@
         <v>77</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5468,7 +5473,7 @@
         <v>77</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="U31" t="s" s="2">
         <v>77</v>
@@ -5504,28 +5509,28 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5533,10 +5538,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5547,7 +5552,7 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>77</v>
@@ -5556,16 +5561,16 @@
         <v>77</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5616,28 +5621,28 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5645,10 +5650,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5659,7 +5664,7 @@
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>77</v>
@@ -5668,19 +5673,19 @@
         <v>77</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5730,28 +5735,28 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>77</v>
@@ -5759,10 +5764,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5773,114 +5778,114 @@
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I34" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="P34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q34" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="R34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH34" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="J34" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="K34" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="L34" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="P34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q34" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="R34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="AG34" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="AI34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5900,22 +5905,22 @@
         <v>77</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5940,13 +5945,13 @@
         <v>77</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>77</v>
@@ -5964,7 +5969,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5976,27 +5981,27 @@
         <v>77</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6004,10 +6009,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>77</v>
@@ -6016,22 +6021,22 @@
         <v>77</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -6080,28 +6085,28 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -6109,10 +6114,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6135,19 +6140,19 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6196,7 +6201,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6208,13 +6213,13 @@
         <v>77</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -6225,10 +6230,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6251,19 +6256,19 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -6312,7 +6317,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6321,19 +6326,19 @@
         <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -6341,10 +6346,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6358,7 +6363,7 @@
         <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>77</v>
@@ -6367,19 +6372,19 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -6428,7 +6433,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6437,19 +6442,19 @@
         <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -6457,10 +6462,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6471,7 +6476,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>77</v>
@@ -6483,13 +6488,13 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>174</v>
+        <v>89</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6540,13 +6545,13 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>77</v>
@@ -6558,7 +6563,7 @@
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -6569,14 +6574,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6595,16 +6600,16 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6642,19 +6647,19 @@
         <v>77</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6666,13 +6671,13 @@
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6683,10 +6688,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6697,31 +6702,31 @@
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6734,7 +6739,7 @@
         <v>77</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>77</v>
@@ -6746,13 +6751,13 @@
         <v>77</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>77</v>
@@ -6770,28 +6775,28 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>77</v>
@@ -6799,10 +6804,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6813,7 +6818,7 @@
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
@@ -6822,19 +6827,19 @@
         <v>77</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6848,7 +6853,7 @@
         <v>77</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>77</v>
@@ -6860,13 +6865,13 @@
         <v>77</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -6884,25 +6889,25 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -6913,10 +6918,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6927,7 +6932,7 @@
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>77</v>
@@ -6936,22 +6941,22 @@
         <v>77</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6964,7 +6969,7 @@
         <v>77</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>77</v>
@@ -7000,25 +7005,25 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -7029,10 +7034,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7052,16 +7057,16 @@
         <v>77</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7076,7 +7081,7 @@
         <v>77</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>77</v>
@@ -7112,7 +7117,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7124,16 +7129,16 @@
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -7141,21 +7146,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>77</v>
@@ -7164,16 +7169,16 @@
         <v>77</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7188,7 +7193,7 @@
         <v>77</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>77</v>
@@ -7224,28 +7229,28 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>77</v>
@@ -7253,21 +7258,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>77</v>
@@ -7276,19 +7281,19 @@
         <v>77</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7302,7 +7307,7 @@
         <v>77</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>77</v>
@@ -7338,25 +7343,25 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -7367,21 +7372,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>77</v>
@@ -7390,16 +7395,16 @@
         <v>77</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7450,28 +7455,28 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>77</v>
@@ -7479,21 +7484,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>77</v>
@@ -7502,16 +7507,16 @@
         <v>77</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7526,7 +7531,7 @@
         <v>77</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>77</v>
@@ -7562,28 +7567,28 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>77</v>
@@ -7591,10 +7596,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7605,7 +7610,7 @@
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>77</v>
@@ -7614,19 +7619,19 @@
         <v>77</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7676,28 +7681,28 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -7705,10 +7710,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7719,7 +7724,7 @@
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>77</v>
@@ -7728,20 +7733,20 @@
         <v>77</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>77</v>
@@ -7754,7 +7759,7 @@
         <v>77</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>77</v>
@@ -7790,28 +7795,28 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
@@ -7819,10 +7824,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7833,7 +7838,7 @@
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>77</v>
@@ -7842,20 +7847,20 @@
         <v>77</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7904,28 +7909,28 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
@@ -7933,10 +7938,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7959,19 +7964,19 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -8020,7 +8025,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8032,13 +8037,13 @@
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>98</v>
+        <v>482</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
@@ -8049,10 +8054,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8063,7 +8068,7 @@
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>77</v>
@@ -8075,13 +8080,13 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8132,13 +8137,13 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>77</v>
@@ -8150,7 +8155,7 @@
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -8161,14 +8166,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8187,16 +8192,16 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8246,7 +8251,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8258,13 +8263,13 @@
         <v>77</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -8275,14 +8280,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8295,25 +8300,25 @@
         <v>77</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -8362,7 +8367,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8374,13 +8379,13 @@
         <v>77</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
@@ -8391,10 +8396,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8405,7 +8410,7 @@
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>77</v>
@@ -8417,17 +8422,17 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8452,13 +8457,13 @@
         <v>77</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>77</v>
@@ -8476,25 +8481,25 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -8505,10 +8510,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8519,7 +8524,7 @@
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>77</v>
@@ -8531,17 +8536,17 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -8590,25 +8595,25 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
@@ -8619,10 +8624,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8645,17 +8650,17 @@
         <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8704,7 +8709,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8716,13 +8721,13 @@
         <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>77</v>
@@ -8733,10 +8738,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8747,7 +8752,7 @@
         <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>77</v>
@@ -8759,17 +8764,17 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -8818,25 +8823,25 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
@@ -8847,10 +8852,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8873,17 +8878,17 @@
         <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -8932,7 +8937,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8944,13 +8949,13 @@
         <v>77</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:00:51+00:00</t>
+    <t>2023-05-09T15:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2241" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2243" uniqueCount="520">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:03:02+00:00</t>
+    <t>2023-05-09T15:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.3.0</t>
+    <t>4.0.1</t>
   </si>
   <si>
     <t>Kind</t>
@@ -274,9 +274,6 @@
     <t>Organization(classCode=ORG, determinerCode=INST)</t>
   </si>
   <si>
-    <t>administrative.group</t>
-  </si>
-  <si>
     <t>Organization.id</t>
   </si>
   <si>
@@ -360,7 +357,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>A human language.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -418,10 +415,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
-</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -475,10 +468,6 @@
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
     <t>Organization.extension:DistrictIndex</t>
   </si>
   <si>
@@ -512,7 +501,7 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -572,6 +561,10 @@
     <t>Organization.identifier.id</t>
   </si>
   <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
     <t>Unique id for inter-element referencing</t>
   </si>
   <si>
@@ -623,7 +616,10 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.3.0</t>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
   </si>
   <si>
     <t>Identifier.use</t>
@@ -657,6 +653,9 @@
     <t>extensible</t>
   </si>
   <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
@@ -757,10 +756,6 @@
     <t>Organization.identifier.type.coding.version</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>Version of the system - if relevant</t>
   </si>
   <si>
@@ -942,7 +937,7 @@
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
   </si>
   <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4B/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>123456</t>
@@ -1221,10 +1216,10 @@
     <t>home</t>
   </si>
   <si>
-    <t>The use of an address (home / work / etc.).</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/address-use|4.3.0</t>
+    <t>The use of an address.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/address-use|4.0.1</t>
   </si>
   <si>
     <t>Address.use</t>
@@ -1248,7 +1243,7 @@
     <t>Distinguishes between physical addresses (those you can visit) and mailing addresses (e.g. PO Boxes and care-of addresses). Most addresses are both.</t>
   </si>
   <si>
-    <t>The definition of Address states that "address is intended to describe postal addresses, not physical locations". However, many applications track whether an address has a dual purpose of being a location that can be visited as well as being a valid delivery destination, and Postal addresses are often used as proxies for physical locations (also see the [Location](http://hl7.org/fhir/R4B/location.html#) resource).</t>
+    <t>The definition of Address states that "address is intended to describe postal addresses, not physical locations". However, many applications track whether an address has a dual purpose of being a location that can be visited as well as being a valid delivery destination, and Postal addresses are often used as proxies for physical locations (also see the [Location](http://hl7.org/fhir/R4/location.html#) resource).</t>
   </si>
   <si>
     <t>both</t>
@@ -1257,7 +1252,7 @@
     <t>The type of an address (physical / postal).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/address-type|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/address-type|4.0.1</t>
   </si>
   <si>
     <t>Address.type</t>
@@ -1509,10 +1504,6 @@
   </si>
   <si>
     <t>Need to keep track of assigned contact points within bigger organization.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-</t>
   </si>
   <si>
     <t>.contactParty</t>
@@ -1977,7 +1968,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="54.10546875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="43.6484375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -2225,15 +2216,15 @@
         <v>30</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2244,28 +2235,28 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>92</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2315,13 +2306,13 @@
         <v>77</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>77</v>
@@ -2344,10 +2335,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2358,25 +2349,25 @@
         <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2427,19 +2418,19 @@
         <v>77</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>99</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
@@ -2456,10 +2447,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2470,28 +2461,28 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I5" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H5" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="J5" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>103</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>104</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2541,19 +2532,19 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
@@ -2570,10 +2561,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2584,7 +2575,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>77</v>
@@ -2596,16 +2587,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2631,43 +2622,43 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>114</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
@@ -2684,21 +2675,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>77</v>
@@ -2710,16 +2701,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>119</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>120</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2769,25 +2760,25 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL7" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>122</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -2798,14 +2789,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2824,16 +2815,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2883,7 +2874,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2895,13 +2886,13 @@
         <v>77</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
@@ -2912,10 +2903,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2923,7 +2914,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>79</v>
@@ -2938,13 +2929,13 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="L9" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2983,17 +2974,17 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -3005,7 +2996,7 @@
         <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
@@ -3022,23 +3013,23 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>77</v>
@@ -3050,13 +3041,13 @@
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="L10" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>145</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -3107,7 +3098,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -3116,10 +3107,10 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
@@ -3136,23 +3127,23 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>77</v>
@@ -3164,13 +3155,13 @@
         <v>77</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3221,7 +3212,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3230,10 +3221,10 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>77</v>
@@ -3250,14 +3241,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3270,25 +3261,25 @@
         <v>77</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L12" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="O12" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -3337,7 +3328,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3349,13 +3340,13 @@
         <v>77</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>77</v>
@@ -3366,10 +3357,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3377,7 +3368,7 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>79</v>
@@ -3389,20 +3380,20 @@
         <v>77</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -3439,19 +3430,19 @@
         <v>77</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3460,65 +3451,65 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AJ13" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>172</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J14" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G14" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J14" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K14" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" t="s" s="2">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
@@ -3567,7 +3558,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3576,30 +3567,30 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK14" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AJ14" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>172</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3610,7 +3601,7 @@
         <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>77</v>
@@ -3622,13 +3613,13 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>89</v>
+        <v>174</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3679,13 +3670,13 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>77</v>
@@ -3697,7 +3688,7 @@
         <v>77</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -3708,14 +3699,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3734,16 +3725,16 @@
         <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3781,19 +3772,19 @@
         <v>77</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3805,13 +3796,13 @@
         <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -3822,10 +3813,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3836,31 +3827,31 @@
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I17" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="J17" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="N17" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3885,47 +3876,49 @@
         <v>77</v>
       </c>
       <c r="X17" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="Z17" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="Y17" s="2"/>
-      <c r="Z17" t="s" s="2">
+      <c r="AA17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="AA17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF17" t="s" s="2">
+      <c r="AG17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3936,10 +3929,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3950,31 +3943,31 @@
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J18" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J18" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K18" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3999,9 +3992,11 @@
         <v>77</v>
       </c>
       <c r="X18" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="Y18" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
         <v>205</v>
       </c>
@@ -4027,19 +4022,19 @@
         <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>207</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -4064,7 +4059,7 @@
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>77</v>
@@ -4076,13 +4071,13 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>89</v>
+        <v>174</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4133,13 +4128,13 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>77</v>
@@ -4151,7 +4146,7 @@
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -4169,7 +4164,7 @@
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4188,16 +4183,16 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4235,19 +4230,19 @@
         <v>77</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4259,13 +4254,13 @@
         <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -4299,7 +4294,7 @@
         <v>77</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
         <v>214</v>
@@ -4375,7 +4370,7 @@
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>220</v>
@@ -4406,7 +4401,7 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>77</v>
@@ -4418,13 +4413,13 @@
         <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>89</v>
+        <v>174</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4475,13 +4470,13 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>77</v>
@@ -4493,7 +4488,7 @@
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -4511,7 +4506,7 @@
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4530,16 +4525,16 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4577,19 +4572,19 @@
         <v>77</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4601,13 +4596,13 @@
         <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -4632,19 +4627,19 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J24" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K24" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>228</v>
@@ -4711,13 +4706,13 @@
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>234</v>
@@ -4748,28 +4743,28 @@
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J25" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K25" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4819,25 +4814,25 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK25" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AG25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK25" t="s" s="2">
+      <c r="AL25" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4848,10 +4843,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4862,29 +4857,29 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J26" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K26" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4894,64 +4889,64 @@
         <v>77</v>
       </c>
       <c r="S26" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="T26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF26" t="s" s="2">
+      <c r="AG26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK26" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="AG26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK26" t="s" s="2">
+      <c r="AL26" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4962,10 +4957,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4976,29 +4971,29 @@
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J27" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K27" t="s" s="2">
-        <v>238</v>
+        <v>174</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -5008,64 +5003,64 @@
         <v>77</v>
       </c>
       <c r="S27" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="T27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF27" t="s" s="2">
+      <c r="AG27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK27" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AG27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK27" t="s" s="2">
+      <c r="AL27" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -5076,10 +5071,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5090,31 +5085,31 @@
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J28" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K28" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -5163,25 +5158,25 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK28" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AG28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK28" t="s" s="2">
+      <c r="AL28" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -5192,10 +5187,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5206,31 +5201,31 @@
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J29" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K29" t="s" s="2">
-        <v>238</v>
+        <v>174</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -5240,64 +5235,64 @@
         <v>77</v>
       </c>
       <c r="S29" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="T29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF29" t="s" s="2">
+      <c r="AG29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK29" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AG29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK29" t="s" s="2">
+      <c r="AL29" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -5308,10 +5303,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5319,104 +5314,104 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J30" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G30" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K30" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T30" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="S30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T30" t="s" s="2">
+      <c r="U30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="U30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF30" t="s" s="2">
+      <c r="AG30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK30" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="AG30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK30" t="s" s="2">
+      <c r="AL30" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -5424,10 +5419,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5435,31 +5430,31 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J31" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G31" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K31" t="s" s="2">
-        <v>238</v>
+        <v>174</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5473,64 +5468,64 @@
         <v>77</v>
       </c>
       <c r="T31" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="U31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF31" t="s" s="2">
+      <c r="AG31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK31" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="AG31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK31" t="s" s="2">
+      <c r="AL31" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AM31" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5538,10 +5533,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5552,25 +5547,25 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J32" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K32" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5621,28 +5616,28 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK32" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AG32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK32" t="s" s="2">
+      <c r="AL32" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AM32" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5650,10 +5645,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5664,28 +5659,28 @@
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J33" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K33" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5735,28 +5730,28 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK33" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AG33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK33" t="s" s="2">
+      <c r="AL33" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>77</v>
@@ -5764,10 +5759,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5778,114 +5773,114 @@
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I34" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I34" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="J34" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="O34" t="s" s="2">
+      <c r="P34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q34" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="P34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q34" t="s" s="2">
+      <c r="R34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK34" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="R34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="AG34" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ34" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK34" t="s" s="2">
+      <c r="AL34" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AL34" t="s" s="2">
+      <c r="AM34" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>333</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5905,22 +5900,22 @@
         <v>77</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5945,14 +5940,14 @@
         <v>77</v>
       </c>
       <c r="X35" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="Y35" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="Y35" t="s" s="2">
+      <c r="Z35" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="Z35" t="s" s="2">
-        <v>341</v>
-      </c>
       <c r="AA35" t="s" s="2">
         <v>77</v>
       </c>
@@ -5969,7 +5964,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5981,27 +5976,27 @@
         <v>77</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AM35" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>344</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6009,34 +6004,34 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J36" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G36" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K36" t="s" s="2">
-        <v>238</v>
+        <v>174</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -6085,28 +6080,28 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AL36" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AL36" t="s" s="2">
+      <c r="AM36" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -6114,10 +6109,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6140,19 +6135,19 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>238</v>
+        <v>174</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6201,7 +6196,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6213,13 +6208,13 @@
         <v>77</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -6230,10 +6225,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6256,19 +6251,19 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -6317,7 +6312,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6326,19 +6321,19 @@
         <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AJ38" t="s" s="2">
+      <c r="AK38" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AK38" t="s" s="2">
+      <c r="AL38" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -6346,10 +6341,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6363,7 +6358,7 @@
         <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>77</v>
@@ -6372,19 +6367,19 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -6433,7 +6428,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6442,19 +6437,19 @@
         <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="AJ39" t="s" s="2">
+      <c r="AK39" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="AK39" t="s" s="2">
+      <c r="AL39" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -6462,10 +6457,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6476,7 +6471,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>77</v>
@@ -6488,13 +6483,13 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>89</v>
+        <v>174</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6545,13 +6540,13 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>77</v>
@@ -6563,7 +6558,7 @@
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -6574,14 +6569,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6600,16 +6595,16 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6647,19 +6642,19 @@
         <v>77</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6671,13 +6666,13 @@
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6688,10 +6683,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6702,31 +6697,31 @@
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I42" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I42" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="J42" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6739,64 +6734,64 @@
         <v>77</v>
       </c>
       <c r="T42" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="Y42" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="U42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X42" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="Y42" t="s" s="2">
+      <c r="Z42" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="Z42" t="s" s="2">
+      <c r="AA42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF42" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AA42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF42" t="s" s="2">
+      <c r="AG42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK42" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AG42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK42" t="s" s="2">
+      <c r="AL42" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AL42" t="s" s="2">
+      <c r="AM42" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>77</v>
@@ -6804,10 +6799,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6818,28 +6813,28 @@
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J43" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J43" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K43" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6853,61 +6848,61 @@
         <v>77</v>
       </c>
       <c r="T43" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="Y43" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="U43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="Y43" t="s" s="2">
+      <c r="Z43" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="Z43" t="s" s="2">
+      <c r="AA43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF43" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AA43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF43" t="s" s="2">
+      <c r="AG43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK43" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AG43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>402</v>
-      </c>
       <c r="AL43" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -6918,10 +6913,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6932,31 +6927,31 @@
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J44" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K44" t="s" s="2">
-        <v>238</v>
+        <v>174</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6969,61 +6964,61 @@
         <v>77</v>
       </c>
       <c r="T44" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="U44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF44" t="s" s="2">
+      <c r="AG44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK44" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="AG44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK44" t="s" s="2">
+      <c r="AL44" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -7034,10 +7029,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7057,16 +7052,16 @@
         <v>77</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>238</v>
+        <v>174</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7081,43 +7076,43 @@
         <v>77</v>
       </c>
       <c r="T45" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7129,16 +7124,16 @@
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AL45" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AL45" t="s" s="2">
+      <c r="AM45" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -7146,39 +7141,39 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J46" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K46" t="s" s="2">
-        <v>238</v>
+        <v>174</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7193,64 +7188,64 @@
         <v>77</v>
       </c>
       <c r="T46" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF46" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="U46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF46" t="s" s="2">
+      <c r="AG46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK46" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AG46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK46" t="s" s="2">
+      <c r="AL46" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AM46" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>77</v>
@@ -7258,42 +7253,42 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J47" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G47" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K47" t="s" s="2">
-        <v>238</v>
+        <v>174</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7307,61 +7302,61 @@
         <v>77</v>
       </c>
       <c r="T47" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF47" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="U47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF47" t="s" s="2">
+      <c r="AG47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK47" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="AG47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK47" t="s" s="2">
+      <c r="AL47" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -7372,39 +7367,39 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J48" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G48" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K48" t="s" s="2">
-        <v>238</v>
+        <v>174</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7455,28 +7450,28 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK48" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="AG48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK48" t="s" s="2">
+      <c r="AL48" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AL48" t="s" s="2">
+      <c r="AM48" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>77</v>
@@ -7484,39 +7479,39 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J49" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K49" t="s" s="2">
-        <v>238</v>
+        <v>174</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7531,64 +7526,64 @@
         <v>77</v>
       </c>
       <c r="T49" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF49" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="U49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF49" t="s" s="2">
+      <c r="AG49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK49" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="AG49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK49" t="s" s="2">
+      <c r="AL49" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="AL49" t="s" s="2">
+      <c r="AM49" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>77</v>
@@ -7596,10 +7591,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7610,28 +7605,28 @@
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J50" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K50" t="s" s="2">
-        <v>238</v>
+        <v>174</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7681,28 +7676,28 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK50" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="AG50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK50" t="s" s="2">
+      <c r="AL50" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AM50" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -7710,10 +7705,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7724,29 +7719,29 @@
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J51" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K51" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>77</v>
@@ -7759,64 +7754,64 @@
         <v>77</v>
       </c>
       <c r="T51" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF51" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="U51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF51" t="s" s="2">
+      <c r="AG51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK51" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="AG51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK51" t="s" s="2">
+      <c r="AL51" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="AL51" t="s" s="2">
-        <v>470</v>
-      </c>
       <c r="AM51" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
@@ -7824,10 +7819,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7838,29 +7833,29 @@
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J52" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K52" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7909,28 +7904,28 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
@@ -7938,10 +7933,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7964,19 +7959,19 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -8025,7 +8020,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8037,13 +8032,13 @@
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>482</v>
+        <v>98</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
@@ -8054,10 +8049,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8068,7 +8063,7 @@
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>77</v>
@@ -8080,13 +8075,13 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>238</v>
+        <v>174</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8137,13 +8132,13 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>77</v>
@@ -8155,7 +8150,7 @@
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -8166,14 +8161,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8192,16 +8187,16 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8251,7 +8246,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8263,13 +8258,13 @@
         <v>77</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -8280,14 +8275,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8300,25 +8295,25 @@
         <v>77</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -8367,7 +8362,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8379,13 +8374,13 @@
         <v>77</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
@@ -8396,10 +8391,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8410,7 +8405,7 @@
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>77</v>
@@ -8422,17 +8417,17 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8457,49 +8452,49 @@
         <v>77</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Y57" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL57" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -8510,10 +8505,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8524,7 +8519,7 @@
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>77</v>
@@ -8536,17 +8531,17 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -8595,25 +8590,25 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
@@ -8624,10 +8619,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8650,17 +8645,17 @@
         <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8709,7 +8704,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8721,13 +8716,13 @@
         <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>77</v>
@@ -8738,10 +8733,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8752,7 +8747,7 @@
         <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>77</v>
@@ -8764,17 +8759,17 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -8823,25 +8818,25 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
@@ -8852,10 +8847,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8878,17 +8873,17 @@
         <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -8937,7 +8932,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8949,13 +8944,13 @@
         <v>77</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T08:50:38+00:00</t>
+    <t>2023-05-10T09:16:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:16:32+00:00</t>
+    <t>2023-05-10T09:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:16:57+00:00</t>
+    <t>2023-05-10T09:45:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:45:15+00:00</t>
+    <t>2023-05-10T09:50:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:50:54+00:00</t>
+    <t>2023-05-10T10:15:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T10:15:35+00:00</t>
+    <t>2023-05-10T10:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T10:16:16+00:00</t>
+    <t>2023-05-10T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:05:21+00:00</t>
+    <t>2023-05-10T11:05:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:05:55+00:00</t>
+    <t>2023-05-10T11:27:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:27:56+00:00</t>
+    <t>2023-05-10T11:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:35:39+00:00</t>
+    <t>2023-05-10T12:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T12:21:05+00:00</t>
+    <t>2023-05-10T12:21:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T12:21:34+00:00</t>
+    <t>2023-05-11T06:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:48:00+00:00</t>
+    <t>2023-05-11T06:54:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:54:25+00:00</t>
+    <t>2023-05-11T08:35:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -536,7 +536,7 @@
     <t>Organizations are known by a variety of ids. Some institutions maintain several, and most collect identifiers for exchange with other organizations concerning the organization.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:system}
+    <t xml:space="preserve">exists:system}
 </t>
   </si>
   <si>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>89</v>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T08:35:45+00:00</t>
+    <t>2023-05-11T08:41:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T08:41:43+00:00</t>
+    <t>2023-05-11T09:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -536,7 +536,7 @@
     <t>Organizations are known by a variety of ids. Some institutions maintain several, and most collect identifiers for exchange with other organizations concerning the organization.</t>
   </si>
   <si>
-    <t xml:space="preserve">exists:system}
+    <t xml:space="preserve">value:system}
 </t>
   </si>
   <si>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>89</v>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T09:08:26+00:00</t>
+    <t>2023-05-11T09:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T09:17:12+00:00</t>
+    <t>2023-05-11T10:17:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:17:25+00:00</t>
+    <t>2023-05-11T10:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:17:56+00:00</t>
+    <t>2023-05-11T10:34:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:34:10+00:00</t>
+    <t>2023-05-11T10:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2595" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2595" uniqueCount="544">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:41:58+00:00</t>
+    <t>2023-05-11T10:56:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -541,9 +541,6 @@
   </si>
   <si>
     <t>Slice based on the type of identifier.</t>
-  </si>
-  <si>
-    <t>openAtEnd</t>
   </si>
   <si>
     <t xml:space="preserve">org-1
@@ -3564,7 +3561,7 @@
         <v>78</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>168</v>
+        <v>141</v>
       </c>
       <c r="AF13" t="s" s="2">
         <v>161</v>
@@ -3576,36 +3573,36 @@
         <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AM13" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="AN13" t="s" s="2">
+      <c r="AO13" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>174</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>161</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>78</v>
@@ -3695,33 +3692,33 @@
         <v>80</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AM14" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>174</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3747,10 +3744,10 @@
         <v>91</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3801,7 +3798,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3810,19 +3807,19 @@
         <v>89</v>
       </c>
       <c r="AI15" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>78</v>
@@ -3833,10 +3830,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3862,10 +3859,10 @@
         <v>137</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>158</v>
@@ -3909,7 +3906,7 @@
         <v>140</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>78</v>
@@ -3918,7 +3915,7 @@
         <v>141</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3939,7 +3936,7 @@
         <v>78</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>78</v>
@@ -3950,10 +3947,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3979,16 +3976,16 @@
         <v>109</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>78</v>
@@ -4016,28 +4013,28 @@
         <v>113</v>
       </c>
       <c r="Y17" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="Z17" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="Z17" t="s" s="2">
+      <c r="AA17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -4058,7 +4055,7 @@
         <v>134</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>78</v>
@@ -4069,10 +4066,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4095,19 +4092,19 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>78</v>
@@ -4132,31 +4129,31 @@
         <v>78</v>
       </c>
       <c r="X18" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="Y18" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="Y18" t="s" s="2">
+      <c r="Z18" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="Z18" t="s" s="2">
+      <c r="AA18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF18" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4174,10 +4171,10 @@
         <v>78</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>78</v>
@@ -4188,10 +4185,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4217,10 +4214,10 @@
         <v>91</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4271,7 +4268,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4280,19 +4277,19 @@
         <v>89</v>
       </c>
       <c r="AI19" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>78</v>
@@ -4303,10 +4300,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4332,10 +4329,10 @@
         <v>137</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>158</v>
@@ -4379,7 +4376,7 @@
         <v>140</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>78</v>
@@ -4388,7 +4385,7 @@
         <v>141</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4409,7 +4406,7 @@
         <v>78</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>78</v>
@@ -4420,10 +4417,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4446,19 +4443,19 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="N21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>78</v>
@@ -4507,7 +4504,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4525,10 +4522,10 @@
         <v>78</v>
       </c>
       <c r="AL21" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>78</v>
@@ -4539,10 +4536,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4568,10 +4565,10 @@
         <v>91</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4622,7 +4619,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4631,19 +4628,19 @@
         <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="AJ22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>78</v>
@@ -4654,10 +4651,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4683,10 +4680,10 @@
         <v>137</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="N23" t="s" s="2">
         <v>158</v>
@@ -4730,7 +4727,7 @@
         <v>140</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>78</v>
@@ -4739,7 +4736,7 @@
         <v>141</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4760,7 +4757,7 @@
         <v>78</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>78</v>
@@ -4771,10 +4768,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4800,16 +4797,16 @@
         <v>103</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>78</v>
@@ -4819,46 +4816,46 @@
         <v>78</v>
       </c>
       <c r="S24" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="T24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4876,10 +4873,10 @@
         <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>78</v>
@@ -4890,10 +4887,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4916,16 +4913,16 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4975,7 +4972,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4993,10 +4990,10 @@
         <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>78</v>
@@ -5007,10 +5004,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5036,14 +5033,14 @@
         <v>109</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -5053,46 +5050,46 @@
         <v>78</v>
       </c>
       <c r="S26" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="T26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5101,7 +5098,7 @@
         <v>89</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>101</v>
@@ -5110,10 +5107,10 @@
         <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>78</v>
@@ -5124,10 +5121,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5150,17 +5147,17 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -5170,46 +5167,46 @@
         <v>78</v>
       </c>
       <c r="S27" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5218,7 +5215,7 @@
         <v>89</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>101</v>
@@ -5227,10 +5224,10 @@
         <v>78</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>78</v>
@@ -5241,10 +5238,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5267,19 +5264,19 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>78</v>
@@ -5328,7 +5325,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5346,10 +5343,10 @@
         <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -5360,10 +5357,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5386,19 +5383,19 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>78</v>
@@ -5408,46 +5405,46 @@
         <v>78</v>
       </c>
       <c r="S29" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="T29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5465,10 +5462,10 @@
         <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -5479,10 +5476,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5508,65 +5505,65 @@
         <v>103</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T30" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="S30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T30" t="s" s="2">
+      <c r="U30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5584,24 +5581,24 @@
         <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO30" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>299</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5624,16 +5621,16 @@
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5647,43 +5644,43 @@
         <v>78</v>
       </c>
       <c r="T31" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="U31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5692,7 +5689,7 @@
         <v>89</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>101</v>
@@ -5701,24 +5698,24 @@
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>310</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5741,13 +5738,13 @@
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5798,7 +5795,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5816,24 +5813,24 @@
         <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>319</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5856,16 +5853,16 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5915,7 +5912,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5933,24 +5930,24 @@
         <v>78</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>329</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5973,26 +5970,26 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="O34" t="s" s="2">
+      <c r="P34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q34" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="P34" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q34" t="s" s="2">
-        <v>335</v>
-      </c>
       <c r="R34" t="s" s="2">
         <v>78</v>
       </c>
@@ -6036,7 +6033,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6051,27 +6048,27 @@
         <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AL34" t="s" s="2">
+      <c r="AM34" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>340</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6094,19 +6091,19 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -6131,14 +6128,14 @@
         <v>78</v>
       </c>
       <c r="X35" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="Y35" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="Y35" t="s" s="2">
+      <c r="Z35" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="Z35" t="s" s="2">
-        <v>348</v>
-      </c>
       <c r="AA35" t="s" s="2">
         <v>78</v>
       </c>
@@ -6155,7 +6152,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6170,27 +6167,27 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AM35" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AM35" t="s" s="2">
-        <v>351</v>
-      </c>
       <c r="AN35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6213,19 +6210,19 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -6274,7 +6271,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6283,7 +6280,7 @@
         <v>89</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>101</v>
@@ -6292,24 +6289,24 @@
         <v>78</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AM36" t="s" s="2">
+      <c r="AN36" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AN36" t="s" s="2">
+      <c r="AO36" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>360</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6332,19 +6329,19 @@
         <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -6393,7 +6390,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6414,7 +6411,7 @@
         <v>78</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -6425,10 +6422,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6451,17 +6448,17 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -6510,7 +6507,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6531,7 +6528,7 @@
         <v>78</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
@@ -6542,10 +6539,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6568,19 +6565,19 @@
         <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -6629,7 +6626,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6641,16 +6638,16 @@
         <v>78</v>
       </c>
       <c r="AJ39" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>78</v>
@@ -6661,10 +6658,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6690,10 +6687,10 @@
         <v>91</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6744,7 +6741,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6753,19 +6750,19 @@
         <v>89</v>
       </c>
       <c r="AI40" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>78</v>
@@ -6776,10 +6773,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6805,10 +6802,10 @@
         <v>137</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>158</v>
@@ -6852,7 +6849,7 @@
         <v>140</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>78</v>
@@ -6861,7 +6858,7 @@
         <v>141</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6882,7 +6879,7 @@
         <v>78</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>78</v>
@@ -6893,10 +6890,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6919,16 +6916,16 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6954,31 +6951,31 @@
         <v>78</v>
       </c>
       <c r="X42" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="Y42" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="Y42" t="s" s="2">
+      <c r="Z42" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="Z42" t="s" s="2">
+      <c r="AA42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF42" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7010,10 +7007,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7036,16 +7033,16 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7095,7 +7092,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7127,10 +7124,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7153,13 +7150,13 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7210,7 +7207,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7242,10 +7239,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7268,16 +7265,16 @@
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7327,7 +7324,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7359,10 +7356,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7388,10 +7385,10 @@
         <v>91</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7442,7 +7439,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7451,19 +7448,19 @@
         <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>78</v>
@@ -7474,10 +7471,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7503,10 +7500,10 @@
         <v>137</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>158</v>
@@ -7550,7 +7547,7 @@
         <v>140</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>78</v>
@@ -7559,7 +7556,7 @@
         <v>141</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7580,7 +7577,7 @@
         <v>78</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>78</v>
@@ -7591,10 +7588,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7620,16 +7617,16 @@
         <v>109</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
@@ -7642,7 +7639,7 @@
         <v>78</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>78</v>
@@ -7657,28 +7654,28 @@
         <v>113</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="Z48" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="Z48" t="s" s="2">
+      <c r="AA48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF48" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7696,24 +7693,24 @@
         <v>78</v>
       </c>
       <c r="AL48" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AN48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>420</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7739,13 +7736,13 @@
         <v>109</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7759,7 +7756,7 @@
         <v>78</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>78</v>
@@ -7774,28 +7771,28 @@
         <v>113</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="Z49" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="Z49" t="s" s="2">
+      <c r="AA49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF49" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7813,10 +7810,10 @@
         <v>78</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>78</v>
@@ -7827,10 +7824,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7853,19 +7850,19 @@
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7878,43 +7875,43 @@
         <v>78</v>
       </c>
       <c r="T50" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7932,10 +7929,10 @@
         <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>78</v>
@@ -7946,10 +7943,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7972,13 +7969,13 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7993,43 +7990,43 @@
         <v>78</v>
       </c>
       <c r="T51" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF51" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8047,28 +8044,28 @@
         <v>78</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO51" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>446</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8087,13 +8084,13 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8108,43 +8105,43 @@
         <v>78</v>
       </c>
       <c r="T52" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8162,28 +8159,28 @@
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>455</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8202,16 +8199,16 @@
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8225,43 +8222,43 @@
         <v>78</v>
       </c>
       <c r="T53" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF53" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8279,10 +8276,10 @@
         <v>78</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
@@ -8293,14 +8290,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8319,13 +8316,13 @@
         <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8376,7 +8373,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8394,28 +8391,28 @@
         <v>78</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO54" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>472</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8434,13 +8431,13 @@
         <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8455,43 +8452,43 @@
         <v>78</v>
       </c>
       <c r="T55" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF55" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8509,24 +8506,24 @@
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO55" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>481</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8549,16 +8546,16 @@
         <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8608,7 +8605,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8626,24 +8623,24 @@
         <v>78</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="AM56" t="s" s="2">
+      <c r="AN56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO56" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>489</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8666,17 +8663,17 @@
         <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
@@ -8689,43 +8686,43 @@
         <v>78</v>
       </c>
       <c r="T57" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF57" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8743,24 +8740,24 @@
         <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="AM57" t="s" s="2">
-        <v>497</v>
-      </c>
       <c r="AN57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8783,17 +8780,17 @@
         <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -8842,7 +8839,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8874,10 +8871,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8900,16 +8897,16 @@
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8959,7 +8956,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8991,10 +8988,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9017,17 +9014,17 @@
         <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -9076,7 +9073,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9094,24 +9091,24 @@
         <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9134,17 +9131,17 @@
         <v>78</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>78</v>
@@ -9193,7 +9190,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9214,7 +9211,7 @@
         <v>78</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>78</v>
@@ -9225,10 +9222,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9251,13 +9248,13 @@
         <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>521</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9308,7 +9305,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9326,10 +9323,10 @@
         <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -9340,10 +9337,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9366,13 +9363,13 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9423,7 +9420,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9432,19 +9429,19 @@
         <v>89</v>
       </c>
       <c r="AI63" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>78</v>
@@ -9455,10 +9452,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9484,10 +9481,10 @@
         <v>137</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>158</v>
@@ -9540,7 +9537,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9561,7 +9558,7 @@
         <v>78</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>78</v>
@@ -9572,14 +9569,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9601,10 +9598,10 @@
         <v>137</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>158</v>
@@ -9659,7 +9656,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9691,10 +9688,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9720,14 +9717,14 @@
         <v>162</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -9776,7 +9773,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9797,7 +9794,7 @@
         <v>78</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>78</v>
@@ -9808,10 +9805,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9834,13 +9831,13 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9867,10 +9864,10 @@
         <v>78</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="Z67" t="s" s="2">
         <v>78</v>
@@ -9891,7 +9888,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>89</v>
@@ -9912,7 +9909,7 @@
         <v>78</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>78</v>
@@ -9923,10 +9920,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9949,17 +9946,17 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -10008,7 +10005,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10029,7 +10026,7 @@
         <v>78</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>78</v>
@@ -10040,10 +10037,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10066,13 +10063,13 @@
         <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10123,7 +10120,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10144,7 +10141,7 @@
         <v>78</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>78</v>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:56:16+00:00</t>
+    <t>2023-05-11T10:56:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:56:44+00:00</t>
+    <t>2023-05-11T11:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:14:34+00:00</t>
+    <t>2023-05-11T11:21:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/performing-organization</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/performing-organization</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:21:30+00:00</t>
+    <t>2023-05-11T11:55:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -471,7 +471,7 @@
     <t>ProvinceIndex</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/performing-organization-province-index}
+    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/performing-organization-province-index}
 </t>
   </si>
   <si>
@@ -487,7 +487,7 @@
     <t>DistrictIndex</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/performing-organization-district-index}
+    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/performing-organization-district-index}
 </t>
   </si>
   <si>
@@ -2039,7 +2039,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="99.38671875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="146.66796875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:55:17+00:00</t>
+    <t>2023-05-11T12:03:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/performing-organization</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/performing-organization</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:03:20+00:00</t>
+    <t>2023-05-11T12:08:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -471,7 +471,7 @@
     <t>ProvinceIndex</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/performing-organization-province-index}
+    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/performing-organization-province-index}
 </t>
   </si>
   <si>
@@ -487,7 +487,7 @@
     <t>DistrictIndex</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/performing-organization-district-index}
+    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/performing-organization-district-index}
 </t>
   </si>
   <si>
@@ -2039,7 +2039,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="146.66796875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="99.38671875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:08:48+00:00</t>
+    <t>2023-05-11T12:16:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:16:35+00:00</t>
+    <t>2023-05-11T12:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:20:22+00:00</t>
+    <t>2023-05-11T12:21:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:21:18+00:00</t>
+    <t>2023-05-11T15:26:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T15:26:02+00:00</t>
+    <t>2023-05-11T16:43:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:43:02+00:00</t>
+    <t>2023-05-11T16:43:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:43:55+00:00</t>
+    <t>2023-05-11T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:57:46+00:00</t>
+    <t>2023-05-11T16:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:58:30+00:00</t>
+    <t>2023-05-11T17:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T17:51:02+00:00</t>
+    <t>2023-05-11T17:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/performing-organization</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/performing-organization</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T17:51:30+00:00</t>
+    <t>2023-05-11T18:15:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -471,7 +471,7 @@
     <t>ProvinceIndex</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/performing-organization-province-index}
+    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/performing-organization-province-index}
 </t>
   </si>
   <si>
@@ -487,7 +487,7 @@
     <t>DistrictIndex</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/performing-organization-district-index}
+    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/performing-organization-district-index}
 </t>
   </si>
   <si>
@@ -2039,7 +2039,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="99.38671875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="142.33984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:15:51+00:00</t>
+    <t>2023-05-11T18:16:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/performing-organization</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/performing-organization</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:16:31+00:00</t>
+    <t>2023-05-11T18:27:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -471,7 +471,7 @@
     <t>ProvinceIndex</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/performing-organization-province-index}
+    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/performing-organization-province-index}
 </t>
   </si>
   <si>
@@ -487,7 +487,7 @@
     <t>DistrictIndex</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/performing-organization-district-index}
+    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/performing-organization-district-index}
 </t>
   </si>
   <si>
@@ -2039,7 +2039,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="142.33984375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="99.38671875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:27:59+00:00</t>
+    <t>2023-05-11T18:29:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:29:46+00:00</t>
+    <t>2023-05-11T18:48:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:48:31+00:00</t>
+    <t>2023-05-11T18:54:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:54:41+00:00</t>
+    <t>2023-05-11T19:02:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:02:34+00:00</t>
+    <t>2023-05-11T19:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:41:30+00:00</t>
+    <t>2023-05-11T19:42:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:42:15+00:00</t>
+    <t>2023-05-11T19:57:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:57:24+00:00</t>
+    <t>2023-05-11T20:23:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:23:29+00:00</t>
+    <t>2023-05-11T20:24:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:24:51+00:00</t>
+    <t>2023-05-11T20:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:42:55+00:00</t>
+    <t>2023-05-12T02:48:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T02:48:54+00:00</t>
+    <t>2023-05-12T02:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T02:49:37+00:00</t>
+    <t>2023-05-12T07:30:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:30:25+00:00</t>
+    <t>2023-05-12T07:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:30:35+00:00</t>
+    <t>2023-05-12T07:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:36:30+00:00</t>
+    <t>2023-05-12T07:54:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:54:06+00:00</t>
+    <t>2023-05-12T07:55:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:55:51+00:00</t>
+    <t>2023-05-12T08:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T08:27:31+00:00</t>
+    <t>2023-05-12T10:26:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:26:59+00:00</t>
+    <t>2023-05-12T10:27:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:27:50+00:00</t>
+    <t>2023-05-12T10:32:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:32:06+00:00</t>
+    <t>2023-05-12T10:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:40:31+00:00</t>
+    <t>2023-05-12T10:53:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:53:52+00:00</t>
+    <t>2023-05-12T13:37:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:37:18+00:00</t>
+    <t>2023-05-12T13:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:51:30+00:00</t>
+    <t>2023-05-12T13:58:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:58:20+00:00</t>
+    <t>2023-05-23T09:07:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T09:07:38+00:00</t>
+    <t>2023-05-23T09:13:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-performing-organization.xlsx
+++ b/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T09:13:26+00:00</t>
+    <t>2023-05-23T09:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
